--- a/test-excel-files/results_test.xlsx
+++ b/test-excel-files/results_test.xlsx
@@ -1,20 +1,20 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
+  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
+  <AppVersion>3.1</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:creator>openpyxl</dc:creator>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-28T00:49:15Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-28T00:49:15Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="1">
@@ -124,7 +124,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -407,13 +407,28 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,20 +444,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>sport</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>timeOrPoints</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>scoreType</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>medal</t>
         </is>
@@ -451,28 +471,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Katie</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ledecky</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+          <t>Goggia</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Alpine Skiing</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>3:59.34</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>1:32.03</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>GOLD</t>
         </is>
@@ -481,28 +506,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Mikaela</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Phelps</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+          <t>Shiffrin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Alpine Skiing</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>4:01.12</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>1:32.47</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>SILVER</t>
         </is>
@@ -511,118 +541,138 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Simone</t>
+          <t>Petra</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Biles</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>15.600</t>
-        </is>
+          <t>Vlhova</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Alpine Skiing</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>1:32.88</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GOLD</t>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BRONZE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nadia</t>
+          <t>Johannes</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Comaneci</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>15.450</t>
-        </is>
+          <t>Boe</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Biathlon</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>23:45.2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SILVER</t>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>GOLD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Usain</t>
+          <t>Marte</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bolt</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>9.63</t>
-        </is>
+          <t>Roeiseland</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Biathlon</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>20:23.1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>GOLD</t>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SILVER</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Serena</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Williams</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+          <t>Chen</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Figure Skating</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>WINS</t>
+          <t>314.56</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>GOLD</t>
         </is>
@@ -631,28 +681,33 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LeBron</t>
+          <t>Yuzuru</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>James</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+          <t>Hanyu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Figure Skating</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>2</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>WINS</t>
+          <t>312.45</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>SILVER</t>
         </is>
@@ -661,88 +716,33 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cristiano</t>
+          <t>Ireen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ronaldo</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+          <t>Wust</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Speed Skating</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>750</t>
-        </is>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>1:43.50</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GOLD</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Lionel</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Messi</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>745</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SILVER</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Maria</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Sharapova</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>WINS</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>GOLD</t>
         </is>
